--- a/docs/DTI/Longlist.xlsx
+++ b/docs/DTI/Longlist.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cubeworks/Documents/DTI Region 7/EMS Dash/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cubeworks/Documents/DTI Region 7/EMS Dash/docs/DTI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB8532A9-7EE4-CB42-8495-12FCD1BD549B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1F321A-91FD-DD40-871D-12FDA9C22FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5180" yWindow="1820" windowWidth="28040" windowHeight="17440" xr2:uid="{6DC4BA1C-A531-2F45-B1FD-86CD51E159E6}"/>
   </bookViews>
@@ -2937,7 +2937,7 @@
         <v>46077</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="136" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" ht="119" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3195,7 +3195,7 @@
         <v>46077</v>
       </c>
     </row>
-    <row r="13" spans="1:30" ht="153" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" ht="136" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3370,7 +3370,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="15" spans="1:30" ht="34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>46080</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="221" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:28" ht="204" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="18" spans="1:28" ht="136" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:28" ht="119" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3714,7 +3714,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="19" spans="1:28" ht="153" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:28" ht="136" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="221" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:28" ht="204" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4230,7 +4230,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="25" spans="1:28" ht="289" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:28" ht="272" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4316,7 +4316,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="187" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:28" ht="170" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="28" spans="1:28" ht="136" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:28" ht="119" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5090,7 +5090,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="35" spans="1:28" ht="221" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:28" ht="187" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5606,7 +5606,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="41" spans="1:28" ht="68" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:28" ht="51" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
